--- a/consent_forms/031_withdrawal_of_consent_form--consent_forms.xlsx
+++ b/consent_forms/031_withdrawal_of_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>witness_1</t>
+          <t>witness 1</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>witness_2</t>
+          <t>witness 2</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>withdraw_consent_1</t>
+          <t>withdraw consent 1</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>withdraw_consent_2</t>
+          <t>withdraw consent 2</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>withdraw_consent_3</t>
+          <t>withdraw consent 3</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>withdraw_consent_4</t>
+          <t>withdraw consent 4</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>withdraw_consent_5</t>
+          <t>withdraw consent 5</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>withdraw_consent_6</t>
+          <t>withdraw consent 6</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>withdraw_consent_7</t>
+          <t>withdraw consent 7</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>withdraw_consent_8</t>
+          <t>withdraw consent 8</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>signature_1</t>
+          <t>signature 1</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>signature_2</t>
+          <t>signature 2</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>signature_3</t>
+          <t>signature 3</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>signature_4</t>
+          <t>signature 4</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>signature_5</t>
+          <t>signature 5</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>signature_6</t>
+          <t>signature 6</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>verification_1</t>
+          <t>verification 1</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>verification_2</t>
+          <t>verification 2</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>verification_3</t>
+          <t>verification 3</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>verification_4</t>
+          <t>verification 4</t>
         </is>
       </c>
     </row>
